--- a/Tasks/EmployeeData.xlsx
+++ b/Tasks/EmployeeData.xlsx
@@ -586,12 +586,12 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Employee creation failed</t>
+          <t>Employee created and document uploaded successfully</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Employee creation failed</t>
+          <t>Employee created and document uploaded successfully</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>AB+</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
@@ -694,14 +694,14 @@
           <t>Daniel_Thompson.pdf</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Success</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Employee creation failed</t>
+          <t>Employee created and document uploaded successfully</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Employee creation failed</t>
+          <t>Employee created and document uploaded successfully</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Employee creation failed</t>
+          <t>Employee created and document uploaded successfully</t>
         </is>
       </c>
     </row>
